--- a/results/[4_flexible_energy_market]_#_inv_cost.xlsx
+++ b/results/[4_flexible_energy_market]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39063.99109145206</v>
+        <v>111810.7469447997</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>61597.35574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>483537.6274462014</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2897240.114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>94331.34471502228</v>
+        <v>189347.2861703724</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>25342.77928792104</v>
+        <v>25760.46244458892</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>23638.06126801545</v>
+        <v>29933.3512337392</v>
       </c>
       <c r="O2" t="n">
-        <v>19940.13531829346</v>
+        <v>19614.29276768806</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30846.52922536713</v>
+        <v>704992.4118705854</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1495599.874611417</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>70193.79982138964</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>56602.42752520426</v>
+        <v>56205.62852636977</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>51649.16401227913</v>
+        <v>99790.74852942684</v>
       </c>
       <c r="O2" t="n">
-        <v>42574.77934331147</v>
+        <v>42884.3297663866</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>242452.4252219552</v>
+        <v>486994.7253484501</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>943335.270081223</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1425.925979620855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>39373.98526588717</v>
+        <v>39337.7908883909</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>26524.46660634092</v>
       </c>
       <c r="N2" t="n">
-        <v>53308.16490721726</v>
+        <v>108849.6084101741</v>
       </c>
       <c r="O2" t="n">
-        <v>30023.09380555204</v>
+        <v>30052.3473966838</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>11578.49752443177</v>
+        <v>13108.7721587798</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76705.58894163162</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1930.947398408091</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>28147.3462746636</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8312.661449003012</v>
+        <v>8317.416250711376</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>825221.7306868637</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/results/[4_flexible_energy_market]_#_inv_cost.xlsx
+++ b/results/[4_flexible_energy_market]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39031.81680257922</v>
+        <v>111810.7469447997</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>61597.35574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>480246.882031777</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2897240.114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>95787.21511094004</v>
+        <v>189347.2861703724</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>25342.77928792126</v>
+        <v>25760.46244458892</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>24790.01698851407</v>
+        <v>29933.3512337392</v>
       </c>
       <c r="O2" t="n">
-        <v>19940.13531829328</v>
+        <v>19614.29276768806</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38474.22754243398</v>
+        <v>704992.4118705854</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1449739.865999208</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>68781.6055373494</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>48766.68152149498</v>
+        <v>56205.62852636977</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>61595.36923039707</v>
+        <v>99790.74852942684</v>
       </c>
       <c r="O2" t="n">
-        <v>37387.51309567104</v>
+        <v>42884.3297663866</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>192739.0887555322</v>
+        <v>486994.7253484501</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>993010.8231553335</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8362.158153921995</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>41828.18095705019</v>
+        <v>39337.7908883909</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>26524.46660634092</v>
       </c>
       <c r="N2" t="n">
-        <v>52911.02090087671</v>
+        <v>108849.6084101741</v>
       </c>
       <c r="O2" t="n">
-        <v>39123.60766563759</v>
+        <v>30052.3473966838</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13108.7721587798</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>8317.416250711376</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>825221.7306868637</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
